--- a/output/渠道资源再配置建议.xlsx
+++ b/output/渠道资源再配置建议.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,42 +444,42 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>净收入占比</t>
+          <t>广告费(元)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>广告费(元)</t>
+          <t>平台佣金(元)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>平台佣金(元)</t>
+          <t>履约费(元)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>履约费(元)</t>
+          <t>渠道毛利率</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>总费用(元)</t>
+          <t>投放ROI</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>渠道毛利率</t>
+          <t>销售费用率</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>销售费用率</t>
+          <t>H2资源调整方向</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>投放回报(毛利/广告费)</t>
+          <t>建议投入幅度</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
@@ -489,15 +489,10 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>H2资源调整方向</t>
+          <t>关键依据</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
-        <is>
-          <t>关键依据</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
         <is>
           <t>数据状态</t>
         </is>
@@ -506,63 +501,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CH01</t>
+          <t>CH03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>自营APP</t>
+          <t>天猫旗舰店</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>自营</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2063657.6</v>
+        <v>2041902.26</v>
       </c>
       <c r="E2" t="n">
-        <v>667713.85</v>
+        <v>400018.13</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0956</v>
+        <v>372096.81</v>
       </c>
       <c r="G2" t="n">
-        <v>385721.93</v>
+        <v>108660.93</v>
       </c>
       <c r="H2" t="n">
-        <v>114483.02</v>
+        <v>120957.75</v>
       </c>
       <c r="I2" t="n">
-        <v>181276.45</v>
+        <v>0.1959046413906217</v>
       </c>
       <c r="J2" t="n">
-        <v>834061.53</v>
+        <v>1.978612635781532</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3236</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.4042</v>
+        <v>0.345772020449206</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>收缩</t>
+        </is>
       </c>
       <c r="M2" t="n">
-        <v>1.7311</v>
+        <v>-0.15</v>
       </c>
       <c r="N2" t="n">
-        <v>-166347.68</v>
+        <v>-306014.54</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>收缩/评估</t>
+          <t>《2026H1渠道销售明细.xlsx》 渠道月度汇总(净收入/毛利);《2026H1线上投放与平台费用.xlsx》 渠道月度费用(广告/佣金/履约);《2026H1线上投放与平台费用.xlsx》 投放明细(支付金额/投放金额)</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
-        <is>
-          <t>净收入占比 9.6%; 毛利率 32.4%; 销售费用率 40.4%; 投放回报 1.73; 渠道净利 -166348 元(亏损)</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -571,63 +563,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CH02</t>
+          <t>CH05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>微信小程序</t>
+          <t>抖音小店</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>自营</t>
+          <t>平台</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1783823.82</v>
+        <v>1563966.84</v>
       </c>
       <c r="E3" t="n">
-        <v>582559.23</v>
+        <v>320246.44</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08260000000000001</v>
+        <v>286138.82</v>
       </c>
       <c r="G3" t="n">
-        <v>165622.24</v>
+        <v>132900.9</v>
       </c>
       <c r="H3" t="n">
-        <v>91594.14999999999</v>
+        <v>92466.50999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>142662</v>
+        <v>0.2047654923425359</v>
       </c>
       <c r="J3" t="n">
-        <v>515606.19</v>
+        <v>1.777478707712571</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3266</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.289</v>
+        <v>0.3805827878038642</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>收缩</t>
+        </is>
       </c>
       <c r="M3" t="n">
-        <v>3.5174</v>
+        <v>-0.15</v>
       </c>
       <c r="N3" t="n">
-        <v>66953.03999999999</v>
+        <v>-274972.42</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>增投</t>
+          <t>《2026H1渠道销售明细.xlsx》 渠道月度汇总(净收入/毛利);《2026H1线上投放与平台费用.xlsx》 渠道月度费用(广告/佣金/履约);《2026H1线上投放与平台费用.xlsx》 投放明细(支付金额/投放金额)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
-        <is>
-          <t>净收入占比 8.3%; 毛利率 32.7%; 销售费用率 28.9%; 投放回报 3.52</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -636,12 +625,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CH03</t>
+          <t>CH04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>天猫旗舰店</t>
+          <t>京东自营</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,49 +639,46 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6387254.38</v>
+        <v>1162383.18</v>
       </c>
       <c r="E4" t="n">
-        <v>2200881.52</v>
+        <v>239715.94</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2958</v>
+        <v>134232.05</v>
       </c>
       <c r="G4" t="n">
-        <v>1021703.4</v>
+        <v>52425.56</v>
       </c>
       <c r="H4" t="n">
-        <v>353130.83</v>
+        <v>67723.42999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>477742.25</v>
+        <v>0.2062279841317043</v>
       </c>
       <c r="J4" t="n">
-        <v>2240493.88</v>
+        <v>3.145879840172299</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3446</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.3508</v>
+        <v>0.2649217102401636</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>维持</t>
+        </is>
       </c>
       <c r="M4" t="n">
-        <v>2.1541</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-39612.36</v>
+        <v>-68224.60000000001</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>维持+优化费用结构</t>
+          <t>《2026H1渠道销售明细.xlsx》 渠道月度汇总(净收入/毛利);《2026H1线上投放与平台费用.xlsx》 渠道月度费用(广告/佣金/履约);《2026H1线上投放与平台费用.xlsx》 投放明细(支付金额/投放金额)</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
-        <is>
-          <t>净收入占比 29.6%; 毛利率 34.5%; 销售费用率 35.1%; 投放回报 2.15; 渠道净利 -39612 元(亏损)</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -701,63 +687,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CH04</t>
+          <t>CH01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>京东自营</t>
+          <t>自营APP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>自营</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2684639.12</v>
+        <v>691728.6599999999</v>
       </c>
       <c r="E5" t="n">
-        <v>925859.97</v>
+        <v>127671.24</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1243</v>
+        <v>143432.05</v>
       </c>
       <c r="G5" t="n">
-        <v>405585.6</v>
+        <v>10517.08</v>
       </c>
       <c r="H5" t="n">
-        <v>175514.71</v>
+        <v>26611.35</v>
       </c>
       <c r="I5" t="n">
-        <v>202507.35</v>
+        <v>0.1845683826372035</v>
       </c>
       <c r="J5" t="n">
-        <v>938233.9399999999</v>
+        <v>1.833265926269617</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3449</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.3495</v>
+        <v>0.291815175042769</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>维持</t>
+        </is>
       </c>
       <c r="M5" t="n">
-        <v>2.2828</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-12373.97</v>
+        <v>-74185.68000000001</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>收缩/评估</t>
+          <t>《2026H1渠道销售明细.xlsx》 渠道月度汇总(净收入/毛利);《2026H1线上投放与平台费用.xlsx》 渠道月度费用(广告/佣金/履约);《2026H1线上投放与平台费用.xlsx》 投放明细(支付金额/投放金额)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
-        <is>
-          <t>净收入占比 12.4%; 毛利率 34.5%; 销售费用率 34.9%; 投放回报 2.28; 渠道净利 -12374 元(亏损)</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -766,63 +749,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CH05</t>
+          <t>CH02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>抖音小店</t>
+          <t>微信小程序</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>平台</t>
+          <t>自营</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6688143.14</v>
+        <v>411486.74</v>
       </c>
       <c r="E6" t="n">
-        <v>2232131.89</v>
+        <v>78941.47</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3097</v>
+        <v>24129.52</v>
       </c>
       <c r="G6" t="n">
-        <v>1096861.93</v>
+        <v>5746.99</v>
       </c>
       <c r="H6" t="n">
-        <v>395755.36</v>
+        <v>15470.77</v>
       </c>
       <c r="I6" t="n">
-        <v>441074.79</v>
+        <v>0.191844505123057</v>
       </c>
       <c r="J6" t="n">
-        <v>2384105.02</v>
+        <v>4.633969511204532</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3337</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.3565</v>
+        <v>0.1373663219378588</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>增投</t>
+        </is>
       </c>
       <c r="M6" t="n">
-        <v>2.035</v>
+        <v>0.2</v>
       </c>
       <c r="N6" t="n">
-        <v>-151973.13</v>
+        <v>22417.05</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>维持+优化费用结构</t>
+          <t>《2026H1渠道销售明细.xlsx》 渠道月度汇总(净收入/毛利);《2026H1线上投放与平台费用.xlsx》 渠道月度费用(广告/佣金/履约);《2026H1线上投放与平台费用.xlsx》 投放明细(支付金额/投放金额)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
-        <is>
-          <t>净收入占比 31.0%; 毛利率 33.4%; 销售费用率 35.6%; 投放回报 2.04; 渠道净利 -151973 元(亏损)</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
@@ -845,49 +825,46 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1989004.87</v>
+        <v>238360.01</v>
       </c>
       <c r="E7" t="n">
-        <v>630211.8</v>
+        <v>48167.69</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0921</v>
+        <v>20271.91</v>
       </c>
       <c r="G7" t="n">
-        <v>274459.1</v>
+        <v>13283.62</v>
       </c>
       <c r="H7" t="n">
-        <v>102841.45</v>
+        <v>22784.48</v>
       </c>
       <c r="I7" t="n">
-        <v>161261.54</v>
+        <v>0.2020795770230082</v>
       </c>
       <c r="J7" t="n">
-        <v>669367.34</v>
+        <v>3.045060381582199</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3168</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.3365</v>
+        <v>0.2782544353811698</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>维持</t>
+        </is>
       </c>
       <c r="M7" t="n">
-        <v>2.2962</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-39155.54</v>
+        <v>-18157.04</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>收缩/评估</t>
+          <t>《2026H1渠道销售明细.xlsx》 渠道月度汇总(净收入/毛利);《2026H1线上投放与平台费用.xlsx》 渠道月度费用(广告/佣金/履约);《2026H1线上投放与平台费用.xlsx》 投放明细(支付金额/投放金额)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
-        <is>
-          <t>净收入占比 9.2%; 毛利率 31.7%; 销售费用率 33.7%; 投放回报 2.30; 渠道净利 -39156 元(亏损)</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>

--- a/output/渠道资源再配置建议.xlsx
+++ b/output/渠道资源再配置建议.xlsx
@@ -521,22 +521,22 @@
         <v>400018.13</v>
       </c>
       <c r="F2" t="n">
-        <v>372096.81</v>
+        <v>369674.83</v>
       </c>
       <c r="G2" t="n">
         <v>108660.93</v>
       </c>
       <c r="H2" t="n">
-        <v>120957.75</v>
+        <v>120957.76</v>
       </c>
       <c r="I2" t="n">
         <v>0.1959046413906217</v>
       </c>
       <c r="J2" t="n">
-        <v>1.978612635781532</v>
+        <v>2.010743604047914</v>
       </c>
       <c r="K2" t="n">
-        <v>0.345772020449206</v>
+        <v>0.3447272152977587</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         <v>-0.15</v>
       </c>
       <c r="N2" t="n">
-        <v>-306014.54</v>
+        <v>-303881.15</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -583,22 +583,22 @@
         <v>320246.44</v>
       </c>
       <c r="F3" t="n">
-        <v>286138.82</v>
+        <v>281881.39</v>
       </c>
       <c r="G3" t="n">
         <v>132900.9</v>
       </c>
       <c r="H3" t="n">
-        <v>92466.50999999999</v>
+        <v>92466.5</v>
       </c>
       <c r="I3" t="n">
         <v>0.2047654923425359</v>
       </c>
       <c r="J3" t="n">
-        <v>1.777478707712571</v>
+        <v>1.827009899447424</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3805827878038642</v>
+        <v>0.3779180254230966</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         <v>-0.15</v>
       </c>
       <c r="N3" t="n">
-        <v>-274972.42</v>
+        <v>-270804.82</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -645,22 +645,22 @@
         <v>239715.94</v>
       </c>
       <c r="F4" t="n">
-        <v>134232.05</v>
+        <v>134260.57</v>
       </c>
       <c r="G4" t="n">
         <v>52425.56</v>
       </c>
       <c r="H4" t="n">
-        <v>67723.42999999999</v>
+        <v>67723.44</v>
       </c>
       <c r="I4" t="n">
         <v>0.2062279841317043</v>
       </c>
       <c r="J4" t="n">
-        <v>3.145879840172299</v>
+        <v>3.042930698119336</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2649217102401636</v>
+        <v>0.2649858371144015</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-68224.60000000001</v>
+        <v>-68299.14</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -701,28 +701,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>691728.6599999999</v>
+        <v>691728.66</v>
       </c>
       <c r="E5" t="n">
         <v>127671.24</v>
       </c>
       <c r="F5" t="n">
-        <v>143432.05</v>
+        <v>148801.35</v>
       </c>
       <c r="G5" t="n">
-        <v>10517.08</v>
+        <v>10517.09</v>
       </c>
       <c r="H5" t="n">
-        <v>26611.35</v>
+        <v>26611.36</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1845683826372035</v>
+        <v>0.1845683826372034</v>
       </c>
       <c r="J5" t="n">
-        <v>1.833265926269617</v>
+        <v>1.881324732604912</v>
       </c>
       <c r="K5" t="n">
-        <v>0.291815175042769</v>
+        <v>0.299576917920388</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-74185.68000000001</v>
+        <v>-79554.7</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -769,22 +769,22 @@
         <v>78941.47</v>
       </c>
       <c r="F6" t="n">
-        <v>24129.52</v>
+        <v>24492.28</v>
       </c>
       <c r="G6" t="n">
         <v>5746.99</v>
       </c>
       <c r="H6" t="n">
-        <v>15470.77</v>
+        <v>15470.78</v>
       </c>
       <c r="I6" t="n">
         <v>0.191844505123057</v>
       </c>
       <c r="J6" t="n">
-        <v>4.633969511204532</v>
+        <v>4.742295123198003</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1373663219378588</v>
+        <v>0.1384154201420925</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>0.2</v>
       </c>
       <c r="N6" t="n">
-        <v>22417.05</v>
+        <v>21985.36</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -831,22 +831,22 @@
         <v>48167.69</v>
       </c>
       <c r="F7" t="n">
-        <v>20271.91</v>
+        <v>20571.48</v>
       </c>
       <c r="G7" t="n">
-        <v>13283.62</v>
+        <v>13283.61</v>
       </c>
       <c r="H7" t="n">
-        <v>22784.48</v>
+        <v>22784.49</v>
       </c>
       <c r="I7" t="n">
         <v>0.2020795770230082</v>
       </c>
       <c r="J7" t="n">
-        <v>3.045060381582199</v>
+        <v>2.96142183255653</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2782544353811698</v>
+        <v>0.2787898020309699</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-18157.04</v>
+        <v>-18284.65</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>

--- a/output/渠道资源再配置建议.xlsx
+++ b/output/渠道资源再配置建议.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="渠道清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +26,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -871,6 +888,124 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+      <formula1>"自营,平台,即时零售"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+      <formula1>"增投,维持,收缩"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+      <formula1>"已确认,待补"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>渠道清单 自查区(只读;公式由 Excel 计算)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>校验项</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>期望/口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>对象行数</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>COUNTA('渠道清单'!A2:A7)</f>
+        <v/>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>应为 6(全量渠道)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>毛利率最大差异</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>MAX(ABS('渠道清单'!I2:I7-'渠道清单'!E2:E7/'渠道清单'!D2:D7))</f>
+        <v/>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>渠道毛利率 = 毛利 ÷ 净收入;应 ≤ 0.0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>枚举违规行数(渠道类型/方向/数据状态)</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUMPRODUCT(--(ISNA(MATCH('渠道清单'!C2:C7,{"自营";"平台";"即时零售"},0))))+SUMPRODUCT(--(ISNA(MATCH('渠道清单'!L2:L7,{"增投";"维持";"收缩"},0))))+SUMPRODUCT(--(ISNA(MATCH('渠道清单'!P2:P7,{"已确认";"待补"},0))))</f>
+        <v/>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>枚举列取值应落在规定集合内;应为 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>提示:销售费用率/渠道净利不可在本表内复算</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>1</f>
+        <v/>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>本表只含广告费/平台佣金/履约费 3 项费用,缺失其余费用项,故这两个指标须回附件复算</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/渠道资源再配置建议.xlsx
+++ b/output/渠道资源再配置建议.xlsx
@@ -889,13 +889,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="C2:C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"自营,平台,即时零售"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"增投,维持,收缩"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="P2:P200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"已确认,待补"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/渠道资源再配置建议.xlsx
+++ b/output/渠道资源再配置建议.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="渠道清单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,21 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,16 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -888,124 +871,11 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
-      <formula1>"自营,平台,即时零售"</formula1>
-    </dataValidation>
-    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
-      <formula1>"增投,维持,收缩"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation sqref="P2:P200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"已确认,待补"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>渠道清单 自查区(只读;公式由 Excel 计算)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>校验项</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>结果</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>期望/口径</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>对象行数</t>
-        </is>
-      </c>
-      <c r="B4" s="3">
-        <f>COUNTA('渠道清单'!A2:A7)</f>
-        <v/>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>应为 6(全量渠道)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>毛利率最大差异</t>
-        </is>
-      </c>
-      <c r="B5" s="3">
-        <f>MAX(ABS('渠道清单'!I2:I7-'渠道清单'!E2:E7/'渠道清单'!D2:D7))</f>
-        <v/>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>渠道毛利率 = 毛利 ÷ 净收入;应 ≤ 0.0005</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>枚举违规行数(渠道类型/方向/数据状态)</t>
-        </is>
-      </c>
-      <c r="B6" s="3">
-        <f>SUMPRODUCT(--(ISNA(MATCH('渠道清单'!C2:C7,{"自营";"平台";"即时零售"},0))))+SUMPRODUCT(--(ISNA(MATCH('渠道清单'!L2:L7,{"增投";"维持";"收缩"},0))))+SUMPRODUCT(--(ISNA(MATCH('渠道清单'!P2:P7,{"已确认";"待补"},0))))</f>
-        <v/>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>枚举列取值应落在规定集合内;应为 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>提示:销售费用率/渠道净利不可在本表内复算</t>
-        </is>
-      </c>
-      <c r="B7" s="3">
-        <f>1</f>
-        <v/>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>本表只含广告费/平台佣金/履约费 3 项费用,缺失其余费用项,故这两个指标须回附件复算</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/渠道资源再配置建议.xlsx
+++ b/output/渠道资源再配置建议.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,27 +434,27 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026H1净收入(元)</t>
+          <t>2026H1 净收入</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>毛利(元)</t>
+          <t>毛利</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>广告费(元)</t>
+          <t>广告费</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>平台佣金(元)</t>
+          <t>平台佣金</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>履约费(元)</t>
+          <t>履约费</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>投放ROI</t>
+          <t>投放 ROI</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -474,27 +474,22 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>H2资源调整方向</t>
+          <t>H2 资源调整方向(增投/维持/收缩)与建议投入幅度</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>建议投入幅度</t>
+          <t>关键依据(2–3 条材料引用)</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>渠道净利(元)</t>
+          <t>数据状态(已确认/待补)</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>关键依据</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>数据状态</t>
+          <t>渠道净利</t>
         </is>
       </c>
     </row>
@@ -530,34 +525,31 @@
         <v>120957.76</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1959046413906217</v>
+        <v>0.1959</v>
       </c>
       <c r="J2" t="n">
-        <v>2.010743604047914</v>
+        <v>2.01</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3447272152977587</v>
+        <v>0.3447</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>收缩</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="N2" t="n">
+          <t>收缩(-15%)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>①《2026H1渠道销售明细.xlsx》Sheet「渠道月度汇总」的 `净收入`/`毛利`;②《2026H1线上投放与平台费用.xlsx》Sheet「渠道月度费用」的 `广告费`/`平台佣金`/`履约费`/`费用合计`/`渠道净利`;③《2026H1线上投放与平台费用.xlsx》Sheet「投放明细」的 `支付金额`/`投放金额`(投放 ROI = 《2026H1线上投放与平台费用.xlsx》Sheet「投放明细」的 `支付金额` ÷ `投放金额`)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>-303881.15</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>《2026H1渠道销售明细.xlsx》 渠道月度汇总(净收入/毛利);《2026H1线上投放与平台费用.xlsx》 渠道月度费用(广告/佣金/履约);《2026H1线上投放与平台费用.xlsx》 投放明细(支付金额/投放金额)</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -592,34 +584,31 @@
         <v>92466.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2047654923425359</v>
+        <v>0.2048</v>
       </c>
       <c r="J3" t="n">
-        <v>1.827009899447424</v>
+        <v>1.83</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3779180254230966</v>
+        <v>0.3779</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>收缩</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="N3" t="n">
+          <t>收缩(-15%)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>①《2026H1渠道销售明细.xlsx》Sheet「渠道月度汇总」的 `净收入`/`毛利`;②《2026H1线上投放与平台费用.xlsx》Sheet「渠道月度费用」的 `广告费`/`平台佣金`/`履约费`/`费用合计`/`渠道净利`;③《2026H1线上投放与平台费用.xlsx》Sheet「投放明细」的 `支付金额`/`投放金额`(投放 ROI = 《2026H1线上投放与平台费用.xlsx》Sheet「投放明细」的 `支付金额` ÷ `投放金额`)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>-270804.82</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>《2026H1渠道销售明细.xlsx》 渠道月度汇总(净收入/毛利);《2026H1线上投放与平台费用.xlsx》 渠道月度费用(广告/佣金/履约);《2026H1线上投放与平台费用.xlsx》 投放明细(支付金额/投放金额)</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -654,34 +643,31 @@
         <v>67723.44</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2062279841317043</v>
+        <v>0.2062</v>
       </c>
       <c r="J4" t="n">
-        <v>3.042930698119336</v>
+        <v>3.04</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2649858371144015</v>
+        <v>0.265</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>维持</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+          <t>维持(0%)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>①《2026H1渠道销售明细.xlsx》Sheet「渠道月度汇总」的 `净收入`/`毛利`;②《2026H1线上投放与平台费用.xlsx》Sheet「渠道月度费用」的 `广告费`/`平台佣金`/`履约费`/`费用合计`/`渠道净利`;③《2026H1线上投放与平台费用.xlsx》Sheet「投放明细」的 `支付金额`/`投放金额`(投放 ROI = 《2026H1线上投放与平台费用.xlsx》Sheet「投放明细」的 `支付金额` ÷ `投放金额`)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>-68299.14</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>《2026H1渠道销售明细.xlsx》 渠道月度汇总(净收入/毛利);《2026H1线上投放与平台费用.xlsx》 渠道月度费用(广告/佣金/履约);《2026H1线上投放与平台费用.xlsx》 投放明细(支付金额/投放金额)</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -716,34 +702,31 @@
         <v>26611.36</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1845683826372034</v>
+        <v>0.1846</v>
       </c>
       <c r="J5" t="n">
-        <v>1.881324732604912</v>
+        <v>1.88</v>
       </c>
       <c r="K5" t="n">
-        <v>0.299576917920388</v>
+        <v>0.2996</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>维持</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+          <t>维持(0%)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>①《2026H1渠道销售明细.xlsx》Sheet「渠道月度汇总」的 `净收入`/`毛利`;②《2026H1线上投放与平台费用.xlsx》Sheet「渠道月度费用」的 `广告费`/`平台佣金`/`履约费`/`费用合计`/`渠道净利`;③《2026H1线上投放与平台费用.xlsx》Sheet「投放明细」的 `支付金额`/`投放金额`(投放 ROI = 《2026H1线上投放与平台费用.xlsx》Sheet「投放明细」的 `支付金额` ÷ `投放金额`)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>-79554.7</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>《2026H1渠道销售明细.xlsx》 渠道月度汇总(净收入/毛利);《2026H1线上投放与平台费用.xlsx》 渠道月度费用(广告/佣金/履约);《2026H1线上投放与平台费用.xlsx》 投放明细(支付金额/投放金额)</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -778,34 +761,31 @@
         <v>15470.78</v>
       </c>
       <c r="I6" t="n">
-        <v>0.191844505123057</v>
+        <v>0.1918</v>
       </c>
       <c r="J6" t="n">
-        <v>4.742295123198003</v>
+        <v>4.74</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1384154201420925</v>
+        <v>0.1384</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>增投</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N6" t="n">
+          <t>增投(+20%)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>①《2026H1渠道销售明细.xlsx》Sheet「渠道月度汇总」的 `净收入`/`毛利`;②《2026H1线上投放与平台费用.xlsx》Sheet「渠道月度费用」的 `广告费`/`平台佣金`/`履约费`/`费用合计`/`渠道净利`;③《2026H1线上投放与平台费用.xlsx》Sheet「投放明细」的 `支付金额`/`投放金额`(投放 ROI = 《2026H1线上投放与平台费用.xlsx》Sheet「投放明细」的 `支付金额` ÷ `投放金额`)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>21985.36</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>《2026H1渠道销售明细.xlsx》 渠道月度汇总(净收入/毛利);《2026H1线上投放与平台费用.xlsx》 渠道月度费用(广告/佣金/履约);《2026H1线上投放与平台费用.xlsx》 投放明细(支付金额/投放金额)</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -840,39 +820,36 @@
         <v>22784.49</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2020795770230082</v>
+        <v>0.2021</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96142183255653</v>
+        <v>2.96</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2787898020309699</v>
+        <v>0.2788</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>维持</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+          <t>维持(0%)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>①《2026H1渠道销售明细.xlsx》Sheet「渠道月度汇总」的 `净收入`/`毛利`;②《2026H1线上投放与平台费用.xlsx》Sheet「渠道月度费用」的 `广告费`/`平台佣金`/`履约费`/`费用合计`/`渠道净利`;③《2026H1线上投放与平台费用.xlsx》Sheet「投放明细」的 `支付金额`/`投放金额`(投放 ROI = 《2026H1线上投放与平台费用.xlsx》Sheet「投放明细」的 `支付金额` ÷ `投放金额`)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>-18284.65</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>《2026H1渠道销售明细.xlsx》 渠道月度汇总(净收入/毛利);《2026H1线上投放与平台费用.xlsx》 渠道月度费用(广告/佣金/履约);《2026H1线上投放与平台费用.xlsx》 投放明细(支付金额/投放金额)</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="P2:P200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="N2:N200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"已确认,待补"</formula1>
     </dataValidation>
   </dataValidations>
